--- a/branches/release-3.0.0/all-profiles.xlsx
+++ b/branches/release-3.0.0/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19264" uniqueCount="1196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19264" uniqueCount="1197">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-codeable-concept</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-codeable-concept</t>
   </si>
   <si>
     <t>Version</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T14:55:19+00:00</t>
+    <t>2026-10-29T04:33:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -354,7 +354,7 @@
     <t>be-ext-radiology-supporting-info-role</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-radiology-supporting-info-role</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-radiology-supporting-info-role</t>
   </si>
   <si>
     <t>BeRadiologySupportingInfoRole</t>
@@ -400,7 +400,7 @@
     <t>ServiceRequest</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-annex-81</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-annex-81</t>
   </si>
   <si>
     <t>diagnostic request
@@ -689,7 +689,7 @@
     <t>validity</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-validity-period}
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-validity-period}
 </t>
   </si>
   <si>
@@ -705,7 +705,7 @@
     <t>latest</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-latest-end-date}
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-latest-end-date}
 </t>
   </si>
   <si>
@@ -721,7 +721,7 @@
     <t>statusReason</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {request-statusReason|5.3.0}
+    <t xml:space="preserve">Extension {request-statusReason|5.4.0}
 </t>
   </si>
   <si>
@@ -761,10 +761,10 @@
     <t>ServiceRequest.extension.value[x]</t>
   </si>
   <si>
-    <t>The actual valueset will be provided when a terminology package is available. For current guidance, see the included [ValueSet](https://www.ehealth.fgov.be/standards/fhir/referral/1.0.0/ValueSet-be-vs-prescription-status-reason.html).</t>
-  </si>
-  <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/referral/ValueSet/be-vs-prescription-status-reason</t>
+    <t>The actual valueset will be provided when a terminology package is available. For current guidance, see the included [ValueSet](https://build.fhir.org/ig/hl7-be/referral-uhmep/ValueSet-be-vs-prescription-status-reason.html).</t>
+  </si>
+  <si>
+    <t>https://www.ehealth.fgov.be/standards/fhir/drp/ValueSet/be-vs-prescription-status-reason</t>
   </si>
   <si>
     <t>ServiceRequest.modifierExtension</t>
@@ -896,7 +896,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/referral/NamingSystem/uhmep</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/drp/NamingSystem/uhmep</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -995,7 +995,7 @@
     <t>ServiceRequest.identifier:SHORT.system</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/referral/NamingSystem/uhmep-short</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/drp/NamingSystem/uhmep-short</t>
   </si>
   <si>
     <t>ServiceRequest.identifier:SHORT.value</t>
@@ -1042,7 +1042,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-annex-81)
+    <t xml:space="preserve">Reference(https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-annex-81)
 </t>
   </si>
   <si>
@@ -1172,7 +1172,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Categories of care that can be prescribed. See [ValueSet](https://www.ehealth.fgov.be/standards/fhir/referral/1.0.0/ValueSet-be-vs-categories-of-care.html).</t>
+    <t>Categories of care that can be prescribed. See [ValueSet](https://build.fhir.org/ig/hl7-be/referral-uhmep/ValueSet-be-vs-categories-of-care.html).</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/servicerequest-category</t>
@@ -1195,7 +1195,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Technical type for Annex 81 prescriptions. See [ValueSet](https://www.ehealth.fgov.be/standards/fhir/referral/1.0.0/ValueSet-be-vs-annex81-technical-type.html).</t>
+    <t>Technical type for Annex 81 prescriptions. See [ValueSet](https://build.fhir.org/ig/hl7-be/referral-uhmep/ValueSet-be-vs-annex81-technical-type.html).</t>
   </si>
   <si>
     <t>ServiceRequest.priority</t>
@@ -2273,7 +2273,7 @@
     <t>ServiceRequest.note.extension.value[x]</t>
   </si>
   <si>
-    <t>Types of notes that can be associated with a prescription. See [ValueSet](https://www.ehealth.fgov.be/standards/fhir/referral/1.0.0/ValueSet-be-vs-note-type.html).</t>
+    <t>Types of notes that can be associated with a prescription. See [ValueSet](https://build.fhir.org/ig/hl7-be/referral-uhmep/ValueSet-be-vs-note-type.html).</t>
   </si>
   <si>
     <t>https://www.ehealth.fgov.be/standards/fhir/terminology/ValueSet/be-vs-note-type</t>
@@ -2368,7 +2368,7 @@
     <t>QuestionnaireResponse</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-imaging-attention-conditions-response</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-imaging-attention-conditions-response</t>
   </si>
   <si>
     <t>Form
@@ -2486,7 +2486,7 @@
     <t>Needed to allow editing of the questionnaire response in a manner that enforces the constraints of the original form.</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/referral/Questionnaire/be-questionnaire-imaging-attention-conditions</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/drp/Questionnaire/be-questionnaire-imaging-attention-conditions</t>
   </si>
   <si>
     <t>QuestionnaireResponse.status</t>
@@ -2768,11 +2768,11 @@
     <t>The diagnostic imaging profile. eReferral version.</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-referral-servicerequest-diagnosticimaging</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-referral-servicerequest-diagnosticimaging</t>
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}prr-1:orderDetail SHALL only be present if code is present {orderDetail.empty() or code.exists()}ereferral-inv-subject-contained:The subject must reference a Patient as contained. {subject.reference.startsWith('#')}ereferral-inv-supportingInfo-safetyChecklist-contained:supportingInfo[safetyChecklist] must reference the contained safety checklist. {supportingInfo.reference.where($this.startsWith('#')).select(substring(1)).all($this in %resource.contained.where(meta.profile contains 'https://www.riziv-inami.be/standards/fhir/ereferral/StructureDefinition/ereferral-imaging-attention-conditions-response').id)}ereferral-inv-status-reason-text-pseudonymized:When statusReason text is present, it must have the be-ext-pseudonymization extension. {extension.where(url = 'http://hl7.org/fhir/StructureDefinition/request-statusReason').value.ofType(CodeableConcept).text.all(extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymization').exists())}ereferral-inv-urgent-requires-urgency-justification:The urgencyJustification extension must be present when priority is urgent. {priority != 'urgent' or extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-urgency-justification').exists()}ereferral-inv-urgency-justification-value-pseudonymized:When urgencyJustification.valueString is present, it must have the be-ext-pseudonymization extension. {extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-urgency-justification').value.ofType(string).all(extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymization').exists())}ereferral-inv-patient-condition-concept-text-pseudonymized:When patientCondition concept text is present, it must have the be-ext-pseudonymization extension. {supportingInfo.extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-codeable-concept').value.ofType(CodeableConcept).text.all(extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymization').exists())}ereferral-inv-patient-condition-code-or-text:patientCondition must contain either a coded indication from the allowed ValueSet or encrypted free text. {supportingInfo.extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-codeable-concept').value.ofType(CodeableConcept).all(coding.exists() or text.exists())}ereferral-inv-contained-patient-birthdate-encrypted:The birthDate of the contained Patient must not be sent in clear text and must be represented only by the encrypted be-ext-pseudonymized-content extension. {contained.ofType(Patient).all(birthDate.hasValue().not() and birthDate.extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymized-content').exists() and birthDate.extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymized-content').extension.where(url = 'encryptedValue').value.matches('^urn:be:fgov:pseudo-encrypted:v1:.+') and birthDate.extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymized-content').extension.where(url = 'marker' and value = true).exists() and birthDate.extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymized-content').extension.where(url = 'format' and value = 'encrypted').exists() and birthDate.extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymized-content').extension.where(url = 'version').value.exists())}ereferral-inv-contained-patient-gender-at-birth-encrypted:The contained Patient genderAtBirth must always be coded as 'other' and must be accompanied by the be-ext-pseudonymized-content encryption extension. {contained.ofType(Patient).extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/core/StructureDefinition/be-ext-gender-at-birth').all(value.ofType(CodeableConcept).coding.where(system = 'http://hl7.org/fhir/administrative-gender' and code = 'other').exists() and value.ofType(CodeableConcept).extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymized-content').extension.where(url = 'encryptedValue').value.matches('^urn:be:fgov:pseudo-encrypted:v1:.+') and value.ofType(CodeableConcept).extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymized-content').extension.where(url = 'marker' and value = true).exists() and value.ofType(CodeableConcept).extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymized-content').extension.where(url = 'format' and value = 'encrypted').exists() and value.ofType(CodeableConcept).extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymized-content').extension.where(url = 'version').value.exists()) and contained.ofType(Patient).extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/core/StructureDefinition/be-ext-gender-at-birth').exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}prr-1:orderDetail SHALL only be present if code is present {orderDetail.empty() or code.exists()}ereferral-inv-subject-contained:The subject must reference a Patient as contained. {subject.reference.startsWith('#')}ereferral-inv-supportingInfo-safetyChecklist-contained:supportingInfo[safetyChecklist] must reference the contained safety checklist. {supportingInfo.reference.where($this.startsWith('#')).select(substring(1)).all($this in %resource.contained.where(meta.profile contains 'https://www.riziv-inami.be/standards/fhir/ereferral/StructureDefinition/ereferral-imaging-attention-conditions-response').id)}ereferral-inv-status-reason-text-pseudonymized:When statusReason text is present, it must have the be-ext-pseudonymization extension. {extension.where(url = 'http://hl7.org/fhir/StructureDefinition/request-statusReason').value.ofType(CodeableConcept).text.all(extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymization').exists())}ereferral-inv-urgent-requires-urgency-justification:The urgencyJustification extension must be present when priority is urgent. {priority != 'urgent' or extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-urgency-justification').exists()}ereferral-inv-urgency-justification-value-pseudonymized:When urgencyJustification.valueString is present, it must have the be-ext-pseudonymization extension. {extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-urgency-justification').value.ofType(string).all(extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymization').exists())}ereferral-inv-patient-condition-concept-text-pseudonymized:When patientCondition concept text is present, it must have the be-ext-pseudonymization extension. {supportingInfo.extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-codeable-concept').value.ofType(CodeableConcept).text.all(extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymization').exists())}ereferral-inv-patient-condition-code-or-text:patientCondition must contain either a coded indication from the allowed ValueSet or encrypted free text. {supportingInfo.extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-codeable-concept').value.ofType(CodeableConcept).all(coding.exists() or text.exists())}ereferral-inv-contained-patient-birthdate-encrypted:The birthDate of the contained Patient must not be sent in clear text and must be represented only by the encrypted be-ext-pseudonymized-content extension. {contained.ofType(Patient).all(birthDate.hasValue().not() and birthDate.extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymized-content').exists() and birthDate.extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymized-content').extension.where(url = 'encryptedValue').value.matches('^urn:be:fgov:pseudo-encrypted:v1:.+') and birthDate.extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymized-content').extension.where(url = 'marker' and value = true).exists() and birthDate.extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymized-content').extension.where(url = 'format' and value = 'encrypted').exists() and birthDate.extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymized-content').extension.where(url = 'version').value.exists())}ereferral-inv-contained-patient-gender-at-birth-encrypted:The contained Patient genderAtBirth must always be coded as 'other' and must be accompanied by the be-ext-pseudonymized-content encryption extension. {contained.ofType(Patient).extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/core/StructureDefinition/be-ext-gender-at-birth').all(value.ofType(CodeableConcept).coding.where(system = 'http://hl7.org/fhir/administrative-gender' and code = 'other').exists() and value.ofType(CodeableConcept).extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymized-content').extension.where(url = 'encryptedValue').value.matches('^urn:be:fgov:pseudo-encrypted:v1:.+') and value.ofType(CodeableConcept).extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymized-content').extension.where(url = 'marker' and value = true).exists() and value.ofType(CodeableConcept).extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymized-content').extension.where(url = 'format' and value = 'encrypted').exists() and value.ofType(CodeableConcept).extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/infsec/StructureDefinition/be-ext-pseudonymized-content').extension.where(url = 'version').value.exists()) and contained.ofType(Patient).extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/core/StructureDefinition/be-ext-gender-at-birth').exists()}</t>
   </si>
   <si>
     <t>ServiceRequest.contained:patient</t>
@@ -2811,7 +2811,7 @@
     <t>feedback</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-feedback-to-prescriber}
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-feedback-to-prescriber}
 </t>
   </si>
   <si>
@@ -2827,7 +2827,7 @@
     <t>performerType</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-performer-type}
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-performer-type}
 </t>
   </si>
   <si>
@@ -2924,7 +2924,7 @@
     <t>urgencyJustification</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-urgency-justification}
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-urgency-justification}
 </t>
   </si>
   <si>
@@ -2940,7 +2940,7 @@
     <t>pssInfo</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-pss-info}
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-pss-info}
 </t>
   </si>
   <si>
@@ -2960,7 +2960,7 @@
     <t>In cases where a request needs to be extended or prolonged, this element can be used to indicate that the current prescription is a continuation of the referenced one. This reference can be a logical reference (with an identifier), or just the display indicating the relevant prescription data, or a literal reference, to an external or contained resource. Usage guidance will be further detailed.</t>
   </si>
   <si>
-    <t>The actual valueset will be provided when a terminology package is available. For current guidance, see the included [ValueSet](https://www.ehealth.fgov.be/standards/fhir/referral/1.0.0/ValueSet-be-vs-request-intent.html).</t>
+    <t>The actual valueset will be provided when a terminology package is available. For current guidance, see the included [ValueSet](https://build.fhir.org/ig/hl7-be/referral-uhmep/ValueSet-be-vs-request-intent.html).</t>
   </si>
   <si>
     <t>3</t>
@@ -3131,7 +3131,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Technical types of prescriptions for routing and workflow. See [ValueSet](https://www.ehealth.fgov.be/standards/fhir/referral/1.0.0/ValueSet-be-vs-prescription-type.html).</t>
+    <t>Technical types of prescriptions for routing and workflow. See [ValueSet](https://build.fhir.org/ig/hl7-be/referral-uhmep/ValueSet-be-vs-prescription-type.html).</t>
   </si>
   <si>
     <t>https://www.ehealth.fgov.be/standards/fhir/terminology/ValueSet/be-vs-prescription-type</t>
@@ -3185,7 +3185,7 @@
     <t>Care setting track (inpatient, ambulatory, urgency)</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/referral/ValueSet/be-vs-request-track</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/drp/ValueSet/be-vs-request-track</t>
   </si>
   <si>
     <t>ServiceRequest.category:track.id</t>
@@ -3227,7 +3227,7 @@
     <t>Priority of the imaging request (routine or urgent)</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/referral/ValueSet/be-vs-imaging-priority</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/drp/ValueSet/be-vs-imaging-priority</t>
   </si>
   <si>
     <t>https://www.ehealth.fgov.be/standards/fhir/terminology/ValueSet/be-vs-diagnostic-imaging-procedure|3.0.0</t>
@@ -3279,7 +3279,7 @@
     <t>Requested performer - typically reference to practitionerroles</t>
   </si>
   <si>
-    <t xml:space="preserve">value:extension('https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-radiology-supporting-info-role').value}
+    <t xml:space="preserve">value:extension('https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-radiology-supporting-info-role').value}
 </t>
   </si>
   <si>
@@ -3317,7 +3317,7 @@
     <t>role</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-radiology-supporting-info-role|3.0.0}
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-radiology-supporting-info-role|3.0.0}
 </t>
   </si>
   <si>
@@ -3462,7 +3462,7 @@
     <t>priorRequestCodeableConcept</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-codeable-concept|3.0.0}
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-codeable-concept|3.0.0}
 </t>
   </si>
   <si>
@@ -3478,7 +3478,7 @@
     <t>ServiceRequest.supportingInfo:priorRequest.extension:priorRequestCodeableConcept.value[x]</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/referral/ValueSet/be-vs-imaging-modality</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/drp/ValueSet/be-vs-imaging-modality</t>
   </si>
   <si>
     <t>ServiceRequest.supportingInfo:priorRequest.extension:role</t>
@@ -3662,7 +3662,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ereferral-inv-patient-condition-strict:A patient condition must contain either free text, or exactly one coding from the allowed ValueSet. Text may accompany a coding. {supportingInfo.where(extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-radiology-supporting-info-role').value = 'patient-condition').extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-codeable-concept').value.ofType(CodeableConcept).all((text.exists() and coding.empty()) or (text.empty() and coding.count() = 1 and memberOf('https://www.ehealth.fgov.be/standards/fhir/terminology/ValueSet/ereferral-vs-imaging-patient-condition-indication')))}</t>
+ereferral-inv-patient-condition-strict:A patient condition must contain either free text, or exactly one coding from the allowed ValueSet. Text may accompany a coding. {supportingInfo.where(extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-radiology-supporting-info-role').value = 'patient-condition').extension.where(url = 'https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-codeable-concept').value.ofType(CodeableConcept).all((text.exists() and coding.empty()) or (text.empty() and coding.count() = 1 and memberOf('https://www.ehealth.fgov.be/standards/fhir/terminology/ValueSet/ereferral-vs-imaging-patient-condition-indication')))}</t>
   </si>
   <si>
     <t>ServiceRequest.supportingInfo:patientCondition.extension:role</t>
@@ -3723,7 +3723,7 @@
     <t>The nursing profile, generic version. Please note the nursing referral for medication does NOT depend on this generic version but is a FHIR prodfile on a different FHIR resource (MedicationRequest)</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-referral-servicerequest-nursing</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-referral-servicerequest-nursing</t>
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
@@ -3746,13 +3746,16 @@
     <t>https://www.ehealth.fgov.be/standards/fhir/terminology/ValueSet/be-vs-nursing-prescription-technical-type</t>
   </si>
   <si>
-    <t>The actual valueset will be provided when a terminology package is available.</t>
+    <t>The actual valueset will be provided when a terminology package is available. For current guidance, see the included [ValueSet](https://build.fhir.org/ig/hl7-be/referral-uhmep/ValueSet-be-vs-requested-services-nurse.html).</t>
   </si>
   <si>
     <t>https://www.ehealth.fgov.be/standards/fhir/terminology/ValueSet/be-vs-nursing-care-requested</t>
   </si>
   <si>
     <t>Details of the nursing activity</t>
+  </si>
+  <si>
+    <t>The actual valueset will be provided when a terminology package is available. For current guidance, see the included [ValueSet](https://build.fhir.org/ig/hl7-be/referral-uhmep/ValueSet-be-vs-requested-services-nurse-detail.html).</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/servicerequest-orderdetail</t>
@@ -4953,16 +4956,16 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="89.84375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="86.66015625" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="32.7734375" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="14.72265625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="186.48046875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="181.6171875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="91.13671875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="106.58203125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="103.3984375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="62.61328125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.7578125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
@@ -57196,10 +57199,10 @@
         <v>182</v>
       </c>
       <c r="Z499" t="s" s="2">
-        <v>1192</v>
+        <v>1195</v>
       </c>
       <c r="AA499" t="s" s="2">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="AB499" t="s" s="2">
         <v>78</v>

--- a/branches/release-3.0.0/all-profiles.xlsx
+++ b/branches/release-3.0.0/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T04:33:29+00:00</t>
+    <t>2026-10-29T04:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release-3.0.0/all-profiles.xlsx
+++ b/branches/release-3.0.0/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T04:45:11+00:00</t>
+    <t>2026-10-29T06:41:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release-3.0.0/all-profiles.xlsx
+++ b/branches/release-3.0.0/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T06:41:01+00:00</t>
+    <t>2026-10-29T06:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release-3.0.0/all-profiles.xlsx
+++ b/branches/release-3.0.0/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T06:43:17+00:00</t>
+    <t>2026-10-29T07:36:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release-3.0.0/all-profiles.xlsx
+++ b/branches/release-3.0.0/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:36:53+00:00</t>
+    <t>2026-10-29T08:00:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
